--- a/AAII_Financials/Quarterly/AEG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AEG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
   <si>
     <t>AEG</t>
   </si>
@@ -656,435 +656,459 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3268600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3298700</v>
+      </c>
+      <c r="F8" s="3">
         <v>3252300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3250000</v>
       </c>
-      <c r="F8" s="3">
-        <v>3906600</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3595400</v>
-      </c>
       <c r="H8" s="3">
+        <v>3661200</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3369500</v>
+      </c>
+      <c r="J8" s="3">
         <v>3323800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3580700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3442600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3466400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3470800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3323500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3656100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3638600</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>1167200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>15958100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8197400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>19566200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>10004400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>39948900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>11644200</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA8" s="3">
         <v>29050900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>47363000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>4127000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>20221100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>18665500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>14526200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>14738800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>17115600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>11262500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>20941900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>16622300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1624600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1639600</v>
+      </c>
+      <c r="F9" s="3">
         <v>2032400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2031000</v>
       </c>
-      <c r="F9" s="3">
-        <v>1978300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1820700</v>
-      </c>
       <c r="H9" s="3">
+        <v>1959500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1803400</v>
+      </c>
+      <c r="J9" s="3">
         <v>2145100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2311000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1970400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1984000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2235500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2140700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2062200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2052400</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>263700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>6500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>627800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>150800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>216900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>253300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>532400</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA9" s="3">
         <v>384000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>470500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>524300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>588200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>82500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>87500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>211600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>-287700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>143600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>314600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>244200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1644000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1659200</v>
+      </c>
+      <c r="F10" s="3">
         <v>1219900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1219100</v>
       </c>
-      <c r="F10" s="3">
-        <v>1928400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1774800</v>
-      </c>
       <c r="H10" s="3">
+        <v>1701700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1566100</v>
+      </c>
+      <c r="J10" s="3">
         <v>1178700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1269800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1472200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1482400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1235200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1182800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1593900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1586300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>903500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>15951500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>7569500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>19415400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>9787600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>39695500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>11111800</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA10" s="3">
         <v>28666900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>46892500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>3602700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>19632900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>18583000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>14438700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>14527300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>17403300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>11118900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>20627400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>16378200</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1120,8 +1144,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,8 +1247,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,109 +1354,121 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F14" s="3">
         <v>-7600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-7600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>4700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>4300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-57500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-61900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>38600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>38800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>38700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-45500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>64400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>64100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>-309100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>120800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-62500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-100200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>59200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>81800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>243900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>135300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-231300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>74700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>-102900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>-116500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>-20300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>-104100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>-32100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>-12100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>25800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>-38700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1453,26 +1497,26 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>39000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>37300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>22900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>22800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>22400</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1524,8 +1568,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1558,210 +1608,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3078400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3106800</v>
+      </c>
+      <c r="F17" s="3">
         <v>3243500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3241200</v>
       </c>
-      <c r="F17" s="3">
-        <v>3480300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3203100</v>
-      </c>
       <c r="H17" s="3">
+        <v>3325900</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3061000</v>
+      </c>
+      <c r="J17" s="3">
         <v>3110100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3350400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3482300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3506300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3579100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3427200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3589500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3572400</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>515500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>16146300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>8439700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>18552800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>9577000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>40318900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>11652500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA17" s="3">
         <v>27998200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>46614700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>4125800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>19557700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>18102100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>13908100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>13960200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>16579800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>10703800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>20412600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>17081300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>190200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>192000</v>
+      </c>
+      <c r="F18" s="3">
         <v>8800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>8800</v>
       </c>
-      <c r="F18" s="3">
-        <v>426300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>392300</v>
-      </c>
       <c r="H18" s="3">
+        <v>335300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>308600</v>
+      </c>
+      <c r="J18" s="3">
         <v>213800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>230300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-39600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-39900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-108300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-103700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>66600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>66300</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>651700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-188200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-242300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1013400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>427400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-370000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-8300</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA18" s="3">
         <v>1052700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>748300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>663500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>563400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>618000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>778600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>535800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>558800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>529400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-459000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1797,187 +1861,195 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-223400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-225400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-294100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-293900</v>
       </c>
-      <c r="F20" s="3">
-        <v>-79300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-73000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-106300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-97800</v>
+      </c>
+      <c r="J20" s="3">
         <v>-232900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-250900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-123800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-124600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-157500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-68300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-20700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-20600</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>56200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-32600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>108800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>100200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>57100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>175500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>123500</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA20" s="3">
         <v>126500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>126100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>142100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>118800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>55000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>54300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>47600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>38400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>37000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>56300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>413600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>417400</v>
+      </c>
+      <c r="F21" s="3">
         <v>302900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>302700</v>
       </c>
-      <c r="F21" s="3">
-        <v>505600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>465300</v>
-      </c>
       <c r="H21" s="3">
+        <v>441600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>406400</v>
+      </c>
+      <c r="J21" s="3">
         <v>446700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>481300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>84100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>84700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>88200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>110300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>109700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>22400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-196700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-72900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>508300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1286900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>774500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>258300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>393400</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>2472000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1447600</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1999,55 +2071,61 @@
       <c r="AI21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>79400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>80100</v>
+      </c>
+      <c r="F22" s="3">
         <v>94500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>94500</v>
       </c>
-      <c r="F22" s="3">
-        <v>103300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>95100</v>
-      </c>
       <c r="H22" s="3">
+        <v>102800</v>
+      </c>
+      <c r="I22" s="3">
+        <v>94600</v>
+      </c>
+      <c r="J22" s="3">
         <v>92700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>99800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>117900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>118700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>123800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>118500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>124500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>123900</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -2100,210 +2178,228 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>343300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>346500</v>
+      </c>
+      <c r="F23" s="3">
         <v>216000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>215900</v>
       </c>
-      <c r="F23" s="3">
-        <v>397500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>365900</v>
-      </c>
       <c r="H23" s="3">
+        <v>334100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>307500</v>
+      </c>
+      <c r="J23" s="3">
         <v>411500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>443300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-72300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-72800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-113300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-108500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-101500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-101000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>707900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-220900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-133500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1113500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>484600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-194500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>115200</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1179300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>874400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>143300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>782300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>618400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>672300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>826300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>574300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>595800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>585700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-424900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>25900</v>
+      </c>
+      <c r="F24" s="3">
         <v>-4100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-4100</v>
       </c>
-      <c r="F24" s="3">
-        <v>42300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>38900</v>
-      </c>
       <c r="H24" s="3">
+        <v>29400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J24" s="3">
         <v>28000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>30100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-37500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-37800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-77400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-74100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-37700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-37500</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>50800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-105500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-70000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>199200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>76200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-46900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-95500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>281500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>186500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>155300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-167800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>204700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-559800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>154000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>240300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>159200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>68400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>165500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2403,210 +2499,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>317600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>320500</v>
+      </c>
+      <c r="F26" s="3">
         <v>220100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>220000</v>
       </c>
-      <c r="F26" s="3">
-        <v>355300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>327000</v>
-      </c>
       <c r="H26" s="3">
+        <v>304800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>280500</v>
+      </c>
+      <c r="J26" s="3">
         <v>383600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>413200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-34800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-35100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-35900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-34400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-63900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-63600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>657100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-115300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-63500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>914300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>408400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-147600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>210700</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA26" s="3">
         <v>992700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>719100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>311100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>577600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1178300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>518400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>585900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>415000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>527300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>420200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-451900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>329600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>332600</v>
+      </c>
+      <c r="F27" s="3">
         <v>210800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>210600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>331800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>305300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>363400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>391500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-48800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-49100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-122800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-122200</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>626800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-152300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-87200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>891700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>396800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-165600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>179600</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA27" s="3">
         <v>949100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>663100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>241300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>510600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>1140000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>480700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>552700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>376600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>490300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>378000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-487100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2706,16 +2820,22 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>29700</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2724,10 +2844,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>50500</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>46500</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2736,37 +2856,37 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>35900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>34400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-44800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-44500</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-431200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>687700</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2807,8 +2927,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2908,8 +3034,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3009,210 +3141,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>223400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>225400</v>
+      </c>
+      <c r="F32" s="3">
         <v>294100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>293900</v>
       </c>
-      <c r="F32" s="3">
-        <v>79300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>73000</v>
-      </c>
       <c r="H32" s="3">
+        <v>106300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>97800</v>
+      </c>
+      <c r="J32" s="3">
         <v>232900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>250900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>123800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>124600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>157500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>68300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>20700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>20600</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>-56200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>32600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-108800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-100200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-57100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-175500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-123500</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-126500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-126100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-142100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-118800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-54300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-47600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-38400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-37000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-56300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-34000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>350700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>354000</v>
+      </c>
+      <c r="F33" s="3">
         <v>230700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>230600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>342900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>315600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>383100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>412700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-27900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-28100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>12200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>11600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-109700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-109200</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>195600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>535300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-87200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>891700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>396800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-165600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>179600</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA33" s="3">
         <v>949100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>663100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>241300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>510600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>1140000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>480700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>552700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>376600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>490300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>378000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-487100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3312,215 +3462,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>350700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>354000</v>
+      </c>
+      <c r="F35" s="3">
         <v>230700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>230600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>342900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>315600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>383100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>412700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-27900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-28100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>12200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>11600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-109700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-109200</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>195600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>535300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-87200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>891700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>396800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-165600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>179600</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA35" s="3">
         <v>949100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>663100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>241300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>510600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>1140000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>480700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>552700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>376600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>490300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>378000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-487100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3556,8 +3724,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3593,109 +3763,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4015800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4052800</v>
+      </c>
+      <c r="F41" s="3">
         <v>708000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>707500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3758100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3458700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1126400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1213500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4172300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4201100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4503200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4312000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4099300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R41" s="3">
         <v>3635800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>7444900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>6916000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>6844800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>8384700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>7667300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>8350200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>11560100</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA41" s="3">
         <v>13377800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>13997200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>10711300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>11275800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>12880700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>13110700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>14265900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>12118600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>12731200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>13282800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>12303900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3795,58 +3973,64 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F43" s="3">
         <v>3562300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3559800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>37600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>34600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3561400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3836700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>60000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>60400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3569100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3417700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>57900</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R43" s="3">
         <v>4826300</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3872,18 +4056,18 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
+      <c r="AB43" s="3">
+        <v>0</v>
       </c>
       <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE43" s="3">
         <v>4912800</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3896,8 +4080,14 @@
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3940,11 +4130,11 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3997,56 +4187,62 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>178568500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>180215600</v>
+      </c>
+      <c r="F45" s="3">
         <v>21556900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>21541700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>17520800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>16125200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>18248300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>19658700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>18858900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>18989100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>21250100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>20348200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>115517500</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>116450800</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
@@ -4098,56 +4294,62 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>182602500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>184286900</v>
+      </c>
+      <c r="F46" s="3">
         <v>28862300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>28842000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>21316500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>19618500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>25934400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>27938900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>23091200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>23250600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>29892800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>28624000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>119674700</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R46" s="3">
         <v>128516600</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
       <c r="S46" s="3">
         <v>0</v>
       </c>
@@ -4199,311 +4401,335 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>185109100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>186816600</v>
+      </c>
+      <c r="F47" s="3">
         <v>325683900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>325454700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>316088100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>290909000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>295148600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>317961200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>292135400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>294152600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>284938700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>272845000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>274390800</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>259741400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>171671400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>172942600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>171162500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>169044200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>164093700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>157439600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>164883900</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA47" s="3">
         <v>159485600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>167846700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>169533700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>161833800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>168698900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>153240900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>155569100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>171034400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>175813600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>186608800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>187632400</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
         <v>395700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>395400</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>412100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>443900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>451000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>431800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R48" s="3">
         <v>513000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2856300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2720300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2692300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2609300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2473600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2378800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>3105400</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA48" s="3">
         <v>3164700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>3215000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>3307500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>2957500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>3202200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>2294900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>2244000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>2211400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>2242900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>2239600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>2232600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>442100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>446200</v>
+      </c>
+      <c r="F49" s="3">
         <v>642200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>641800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>616600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>567400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>604600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>651300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>610700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>615000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>579200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>554600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>400700</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>448900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1440600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1429800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1415000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1508700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1541500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1382400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1561000</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA49" s="3">
         <v>3401500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1912200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>4231100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1932800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1953400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1863000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1869600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>2021400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>2042000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>2024800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>2118700</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4603,8 +4829,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4704,109 +4936,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4103700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4141600</v>
+      </c>
+      <c r="F52" s="3">
         <v>677500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>677000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>10804500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>9943800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>646000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>696000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>6378400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>6422500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>652100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>624500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>7175800</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" s="3">
         <v>629500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>270200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X52" s="3">
         <v>143600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA52" s="3">
         <v>211600</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC52" s="3">
         <v>153100</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
         <v>6439100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>5808300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2574100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>9734900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>9921800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>10226200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>10604200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4906,109 +5150,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>385839100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>389398100</v>
+      </c>
+      <c r="F54" s="3">
         <v>372470400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>372208100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>364809200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>335749000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>338948100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>365146100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>338444200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>340781100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>333349200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>319200900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>418409400</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R54" s="3">
         <v>406633500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>506722900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>500182200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>495033700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>494741900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>476820500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>443711300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>461448300</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA54" s="3">
         <v>480592800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>495536400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>481459000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>457491400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>474043300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>439933200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>448162700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>467149600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>477894800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>499290600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>499808300</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5044,8 +5300,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5081,56 +5339,58 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>229600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>231800</v>
+      </c>
+      <c r="F57" s="3">
         <v>229000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>228800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>238400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>219400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>313700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>337900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>532500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>536200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>672000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>643500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>230300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R57" s="3">
         <v>288600</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
@@ -5182,58 +5442,64 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>2017100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2015700</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>2041600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2199400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>2709200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2594200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>1380800</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5256,21 +5522,21 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE58" s="3">
         <v>2112500</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5283,157 +5549,169 @@
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>156597700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>158042200</v>
+      </c>
+      <c r="F59" s="3">
         <v>364000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>363700</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>452400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>487400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>427500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>430500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1658000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1587600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>91515300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>95140500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>432972700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>422263300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>417916900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>417450600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>402363700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>369773100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>376985000</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA59" s="3">
         <v>405208700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>415096000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>405439800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>383724000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>391384700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>357369400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>367006600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>377844900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>387177400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>395586900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>391081800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>156827400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>158274000</v>
+      </c>
+      <c r="F60" s="3">
         <v>3609300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3606700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>238400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>219400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3733300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4021900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>960000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>966700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5999800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5745100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>91745600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R60" s="3">
         <v>97745000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
       <c r="S60" s="3">
         <v>0</v>
       </c>
@@ -5485,210 +5763,228 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4381400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4421800</v>
+      </c>
+      <c r="F61" s="3">
         <v>4330200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4327100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5012300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4613100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5094700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5488500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4952300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4986500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>5360900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>5133400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5889700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>5866200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>12947900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>12790600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>12659000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>12447900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>11808300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>10707100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>11666000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>12709100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>12874200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>16639000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>17513100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>15359200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>17281900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>17472400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>17503200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>15793100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>16121100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>15254800</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>214363100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>216340400</v>
+      </c>
+      <c r="F62" s="3">
         <v>352766200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>352517900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>348533200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>320769600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>319809500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>344528200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>323303300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>325535700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>310617900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>297434400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>309586200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3">
         <v>290767300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>6123200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X62" s="3">
         <v>6300600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA62" s="3">
         <v>6279300</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC62" s="3">
         <v>5643500</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3">
         <v>12105500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>5512500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>2596200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>9855600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>17896900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>10355400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>10723900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5788,8 +6084,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5889,8 +6191,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5990,109 +6298,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>375571800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>379036100</v>
+      </c>
+      <c r="F66" s="3">
         <v>361322100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>361067700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>353783900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>325602000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>329306300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>354759100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>329215700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>331488800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>322787700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>309087600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>407221600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R66" s="3">
         <v>394948200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>477927700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>471940500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>467082800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>466545400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>450784200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>418393300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>433973000</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA66" s="3">
         <v>453298200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>466508700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>453482700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>429517800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>444896700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>413468200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>421372000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>439360300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>450169300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>470018200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>469565100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6128,8 +6448,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6229,8 +6551,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6330,8 +6658,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6431,8 +6765,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6532,109 +6872,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4448800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4489800</v>
+      </c>
+      <c r="F72" s="3">
         <v>4975900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4972400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4795100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4413100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4500500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4848300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3963400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3990700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>5636100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>5396900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>7116800</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R72" s="3">
         <v>8303900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>14005900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>13102900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>12968000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>12935700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>11898300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>10363000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>11930700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA72" s="3">
         <v>12476700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>12489000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>12633300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>11787500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>12015800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>9744700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>9903100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>10237800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>8979300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>9437400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>9470300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6734,8 +7086,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6835,8 +7193,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6936,109 +7300,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10185100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10279000</v>
+      </c>
+      <c r="F76" s="3">
         <v>11048500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11040700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>10872600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10006500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>9511300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10246500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9098900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9161700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>10418900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9976700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11009800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>11688400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>11497300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>28795300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>28241600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>27950900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>28196500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>26036300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>25318000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>27475300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>25927700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>27294600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>29027600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>27976300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>27973600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>29146600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>26465000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>26790600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>27789300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>27725500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>29272500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>30243200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7138,215 +7514,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>350700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>354000</v>
+      </c>
+      <c r="F81" s="3">
         <v>230700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>230600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>342900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>315600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>383100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>412700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-27900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-28100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>12200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>11600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-109700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-109200</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>195600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>535300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-87200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>891700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>396800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-165600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>179600</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA81" s="3">
         <v>949100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>663100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>241300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>510600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>1140000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>480700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>552700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>376600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>490300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>378000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-487100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7382,86 +7776,88 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-42900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="F83" s="3">
         <v>-13500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>-14500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>-20400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>-20500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>-23200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>-30700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>-73100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>-72800</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>207900</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>366600</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3">
         <v>-904500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>148000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>641800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>173400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>289900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>452800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>278200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA83" s="3">
         <v>1292700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>573200</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>8</v>
       </c>
@@ -7474,17 +7870,23 @@
       <c r="AF83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>0</v>
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7584,8 +7986,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7685,8 +8093,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7786,8 +8200,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7887,8 +8307,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7988,109 +8414,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>666100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>672200</v>
+      </c>
+      <c r="F89" s="3">
         <v>358100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>357900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-103300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-95100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>59500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>64100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>346600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>349000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-108900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-104300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>579100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>576400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S89" s="3">
         <v>2015500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>618000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1099500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>140000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1558400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-2055600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-823100</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA89" s="3">
         <v>7965800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>6960100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1825200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-1144600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>496400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-653500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>3129000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-2302500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>102100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>685500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-181900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8126,109 +8564,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-8800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-15300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-14100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-15000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-16200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-11800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-11900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-20400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-19600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-15300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-15200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S91" s="3">
         <v>-31000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-19000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-19000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-16000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-10600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-52900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-28000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-111300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-52500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-82100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-16600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-23100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-32500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-28200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-56300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8328,8 +8774,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8429,109 +8881,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>125100</v>
+      </c>
+      <c r="F94" s="3">
         <v>440900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>440600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>152100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>140000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>97300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>104800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>60000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>60400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1175000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1125100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>71000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>70600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S94" s="3">
         <v>562000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-58800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-6500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-34500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>40200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-239400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>104800</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-93800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>101600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-427500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-104700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-14400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-1069900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-109800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-359000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>9400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-906200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8567,109 +9031,117 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F96" s="3">
         <v>369300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>369000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>20000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>18400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>286800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>308900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>18800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>18900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>162500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>155600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>144700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>144000</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="R96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-1100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-62800</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-337100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-198500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-197200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-196500</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-167200</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-180800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8769,8 +9241,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8870,8 +9348,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8971,307 +9455,331 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-223400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-225400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1070800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-123900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-114000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-401700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-432700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-524500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-528100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-978800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-937200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-802400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-798600</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S100" s="3">
         <v>-681900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-5400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-429700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>526600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>227500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-376000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-416200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-4069100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-3278100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-2435300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-478800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1573000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-189400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>104100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>2098300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-157100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>625600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>961400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-82200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-75700</v>
+      </c>
+      <c r="F101" s="3">
         <v>22800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>24500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>23600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>23700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-9900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-9500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-10900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-10900</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>60800</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
         <v>14400</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3">
         <v>-58400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>25000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-3200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-10800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>60300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-88800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-33200</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA101" s="3">
         <v>36000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>8600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>32900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-14400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-50900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-124100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-28500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>151500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-31700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>589500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>594900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-274200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-274000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-157400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-144800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-222100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-239200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-94300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-94900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2272600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-2176100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-163200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-162400</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>1837200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>578900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1538900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>621400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1230500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-2759800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1167600</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA102" s="3">
         <v>3838900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>3782400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1029000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1695200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1230900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-908200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>2039100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-342600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>51600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>976600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-125600</v>
       </c>
     </row>
